--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,21 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -462,7 +477,16 @@
       <c r="D2" t="n">
         <v>99</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>튀김 재료</t>
         </is>
@@ -487,7 +511,16 @@
       <c r="D3" t="n">
         <v>99</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>신선 재료</t>
         </is>
@@ -512,7 +545,16 @@
       <c r="D4" t="n">
         <v>99</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>보존 식품</t>
         </is>
@@ -537,7 +579,16 @@
       <c r="D5" t="n">
         <v>99</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>무기 제작 재료</t>
         </is>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -488,6 +493,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>튀김 재료</t>
         </is>
       </c>
@@ -520,7 +530,7 @@
       <c r="G3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>신선 재료</t>
         </is>
@@ -556,6 +566,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>보존 식품</t>
         </is>
       </c>
@@ -588,7 +603,7 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>무기 제작 재료</t>
         </is>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,74 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>무기 제작 재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>meat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>고기</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>99</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>추적자(monster_b) 드롭</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cheese</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>치즈</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>날쌘이(monster_c) 드롭</t>
         </is>
       </c>
     </row>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,40 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>날쌘이(monster_c) 드롭</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>토마토</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>99</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>폐허 채집</t>
         </is>
       </c>
     </row>
